--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487715_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487715_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>D. EBOLO OLU-ELIJAH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3929</v>
+        <v>7.0887</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1664</v>
+        <v>5.137</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2265</v>
+        <v>1.9517</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0005</v>
+        <v>4.5967</v>
       </c>
       <c r="H2" t="n">
-        <v>2.278</v>
+        <v>2.0391</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2775</v>
+        <v>2.5576</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2872</v>
+        <v>5.399</v>
       </c>
       <c r="K2" t="n">
-        <v>3.003</v>
+        <v>2.1462</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2842</v>
+        <v>3.2528</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2867</v>
+        <v>-0.8023</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.725</v>
+        <v>-0.1071</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5617</v>
+        <v>-0.6952</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5523</v>
+        <v>2.7164</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5224</v>
+        <v>2.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8984</v>
+        <v>0.3875</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0031</v>
+        <v>0.2619</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8953</v>
+        <v>0.1256</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9418</v>
+        <v>-0.6119</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8462</v>
+        <v>-0.3299</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0955</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. EBOLO OLU-ELIJAH</t>
+          <t>L. VALERA VILLEGAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1611</v>
+        <v>7.0592</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9368</v>
+        <v>6.3199</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2243</v>
+        <v>0.7393</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5967</v>
+        <v>4.6523</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0391</v>
+        <v>2.1231</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5576</v>
+        <v>2.5292</v>
       </c>
       <c r="J3" t="n">
-        <v>5.399</v>
+        <v>5.0316</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1462</v>
+        <v>2.3522</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2528</v>
+        <v>2.6794</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8023</v>
+        <v>-0.3792</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1071</v>
+        <v>-0.229</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6952</v>
+        <v>-0.1502</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7164</v>
+        <v>2.3284</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.194</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9105</v>
+        <v>2.5224</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4599</v>
+        <v>0.0785</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0617</v>
+        <v>-0.0236</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3982</v>
+        <v>0.1021</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3299</v>
+        <v>1.506</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2821</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. VALERA VILLEGAS</t>
+          <t>A. ARMSTRONG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.8224</v>
+        <v>6.0116</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9195</v>
+        <v>4.8173</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9029</v>
+        <v>1.1943</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6523</v>
+        <v>3.8979</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1231</v>
+        <v>2.442</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5292</v>
+        <v>1.4559</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0316</v>
+        <v>4.3436</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3522</v>
+        <v>2.3316</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6794</v>
+        <v>2.0121</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3792</v>
+        <v>-0.4458</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.229</v>
+        <v>0.1104</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1502</v>
+        <v>-0.5561</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3284</v>
+        <v>2.7164</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.194</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5224</v>
+        <v>2.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1584</v>
+        <v>-0.2728</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.424</v>
+        <v>-0.2263</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2656</v>
+        <v>-0.0465</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="W4" t="n">
-        <v>1.506</v>
+        <v>0.894</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.506</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ARMSTRONG</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.3204</v>
+        <v>5.71</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3168</v>
+        <v>3.8651</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0035</v>
+        <v>1.8449</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8979</v>
+        <v>2.0005</v>
       </c>
       <c r="H5" t="n">
-        <v>2.442</v>
+        <v>2.278</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4559</v>
+        <v>-0.2775</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3436</v>
+        <v>3.2872</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3316</v>
+        <v>3.003</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0121</v>
+        <v>0.2842</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4458</v>
+        <v>-1.2867</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1104</v>
+        <v>-0.725</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5561</v>
+        <v>-0.5617</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7164</v>
+        <v>1.5523</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9105</v>
+        <v>2.5224</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9641</v>
+        <v>1.2155</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7268</v>
+        <v>0.7018</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2373</v>
+        <v>0.5137</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3299</v>
+        <v>0.9418</v>
       </c>
       <c r="W5" t="n">
-        <v>0.894</v>
+        <v>0.8462</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2239</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3858</v>
+        <v>2.7213</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8892</v>
+        <v>3.0884</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5033</v>
+        <v>-0.3671</v>
       </c>
       <c r="G6" t="n">
         <v>3.0631</v>
@@ -922,13 +922,13 @@
         <v>2.3284</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3824</v>
+        <v>-0.2821</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7896</v>
+        <v>-0.0112</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4071</v>
+        <v>-0.2708</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2239</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3489</v>
+        <v>2.6398</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8921</v>
+        <v>0.9922</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4568</v>
+        <v>1.6475</v>
       </c>
       <c r="G7" t="n">
         <v>2.2823</v>
@@ -1000,13 +1000,13 @@
         <v>1.3582</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3214</v>
+        <v>-0.0306</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1817</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1397</v>
+        <v>0.051</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6817</v>
+        <v>2.1093</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1338</v>
+        <v>1.5342</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5478</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>1.2878</v>
@@ -1078,13 +1078,13 @@
         <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3822</v>
+        <v>0.0454</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3028</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0794</v>
+        <v>-0.0521</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5809</v>
+        <v>1.8083</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7513</v>
+        <v>1.9515</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1704</v>
+        <v>-0.1432</v>
       </c>
       <c r="G9" t="n">
         <v>3.1723</v>
@@ -1156,13 +1156,13 @@
         <v>1.5523</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3093</v>
+        <v>-0.0819</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6662</v>
+        <v>-0.466</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3569</v>
+        <v>0.3842</v>
       </c>
       <c r="V9" t="n">
         <v>-0.894</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4289</v>
+        <v>1.1202</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4593</v>
+        <v>1.9598</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0304</v>
+        <v>-0.8396</v>
       </c>
       <c r="G10" t="n">
         <v>1.8682</v>
@@ -1234,13 +1234,13 @@
         <v>1.9403</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7095</v>
+        <v>-0.0182</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3028</v>
+        <v>0.1977</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4067</v>
+        <v>-0.2159</v>
       </c>
       <c r="V10" t="n">
         <v>-1.506</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7024</v>
+        <v>-0.3203</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3334</v>
+        <v>-1.0331</v>
       </c>
       <c r="F11" t="n">
-        <v>0.631</v>
+        <v>0.7128</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2178</v>
@@ -1312,13 +1312,13 @@
         <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.3154</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1211</v>
+        <v>0.1792</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0545</v>
+        <v>0.1363</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2062</v>
+        <v>-0.8242</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.355</v>
+        <v>-1.0547</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1488</v>
+        <v>0.2305</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1074</v>
@@ -1390,13 +1390,13 @@
         <v>2.1344</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3212</v>
+        <v>0.0608</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5451</v>
+        <v>-0.2448</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2239</v>
+        <v>0.3056</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7623</v>
+        <v>-2.6722</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.578</v>
+        <v>-4.3788</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8157</v>
+        <v>1.7067</v>
       </c>
       <c r="G13" t="n">
         <v>-4.0183</v>
@@ -1468,13 +1468,13 @@
         <v>2.7164</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0381</v>
+        <v>1.1283</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3358</v>
+        <v>0.535</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7023</v>
+        <v>0.5933</v>
       </c>
       <c r="V13" t="n">
         <v>2.3522</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>32.4521</v>
+        <v>32.4517</v>
       </c>
       <c r="E14" t="n">
         <v>23.1988</v>
       </c>
       <c r="F14" t="n">
-        <v>9.2532</v>
+        <v>9.2529</v>
       </c>
       <c r="G14" t="n">
         <v>20.4776</v>
@@ -1546,7 +1546,7 @@
         <v>25.2242</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5461</v>
+        <v>2.5458</v>
       </c>
       <c r="T14" t="n">
         <v>0.9197</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4611</v>
+        <v>0.6341</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4417</v>
+        <v>1.6419</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9806</v>
+        <v>-1.0078</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4355</v>
@@ -1624,13 +1624,13 @@
         <v>0.5821</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2974</v>
+        <v>-0.1245</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1817</v>
+        <v>0.0185</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1157</v>
+        <v>-0.143</v>
       </c>
       <c r="V15" t="n">
         <v>0.6119</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4292</v>
+        <v>2.229</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3587</v>
+        <v>-2.1407</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1086</v>
@@ -1702,13 +1702,13 @@
         <v>1.9403</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3268</v>
+        <v>-0.309</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2412</v>
+        <v>-0.4414</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0857</v>
+        <v>0.1324</v>
       </c>
       <c r="V16" t="n">
         <v>1.506</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SANCHEZ SANCHEZ</t>
+          <t>C. CUESTA DE SANTOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.16</v>
+        <v>0.0303</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8379</v>
+        <v>2.7315</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9979</v>
+        <v>-2.7012</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0851</v>
+        <v>1.1338</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0017</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0868</v>
+        <v>1.0555</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2826</v>
+        <v>5.8196</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3182</v>
+        <v>1.3718</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0356</v>
+        <v>4.4479</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1975</v>
+        <v>-4.6858</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3198</v>
+        <v>-1.2935</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1223</v>
+        <v>-3.3924</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7761</v>
+        <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3331</v>
+        <v>-0.0572</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2434</v>
+        <v>-0.1015</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5765</v>
+        <v>0.0443</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2821</v>
+        <v>0.894</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2821</v>
+        <v>0.894</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. CUESTA DE SANTOS</t>
+          <t>M. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4152</v>
+        <v>-0.4241</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5313</v>
+        <v>0.4375</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.9465</v>
+        <v>-0.8616</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1338</v>
+        <v>0.0851</v>
       </c>
       <c r="H18" t="n">
-        <v>0.07829999999999999</v>
+        <v>-0.0017</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0555</v>
+        <v>0.0868</v>
       </c>
       <c r="J18" t="n">
-        <v>5.8196</v>
+        <v>1.2826</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3718</v>
+        <v>1.3182</v>
       </c>
       <c r="L18" t="n">
-        <v>4.4479</v>
+        <v>-0.0356</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.6858</v>
+        <v>-1.1975</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2935</v>
+        <v>-1.3198</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.3924</v>
+        <v>0.1223</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.9403</v>
+        <v>-0.194</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9403</v>
+        <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5027</v>
+        <v>-0.5972</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3017</v>
+        <v>-0.157</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.201</v>
+        <v>-0.4402</v>
       </c>
       <c r="V18" t="n">
-        <v>0.894</v>
+        <v>0.2821</v>
       </c>
       <c r="W18" t="n">
-        <v>0.894</v>
+        <v>0.2821</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.7994</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9633</v>
+        <v>0.7631</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.617</v>
+        <v>-1.5625</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1884</v>
@@ -1936,13 +1936,13 @@
         <v>0.194</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0004</v>
+        <v>-0.1452</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3645</v>
+        <v>0.1643</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3641</v>
+        <v>-0.3095</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6597</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1851</v>
+        <v>-2.3125</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1077</v>
+        <v>-1.2078</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0774</v>
+        <v>-1.1046</v>
       </c>
       <c r="G20" t="n">
         <v>-2.9309</v>
@@ -2014,13 +2014,13 @@
         <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3333</v>
+        <v>-0.4607</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1828</v>
+        <v>0.0827</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5161</v>
+        <v>-0.5434</v>
       </c>
       <c r="V20" t="n">
         <v>2.8254</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4037</v>
+        <v>-3.4493</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8794</v>
+        <v>-1.9795</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5244</v>
+        <v>-1.4699</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9006</v>
@@ -2092,13 +2092,13 @@
         <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>0.255</v>
+        <v>0.2094</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.12</v>
+        <v>-0.2201</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3751</v>
+        <v>0.4296</v>
       </c>
       <c r="V21" t="n">
         <v>0.0478</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
+          <t>J. VILASANCHEZ FREIJOMIL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9614</v>
+        <v>-4.3848</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9978</v>
+        <v>-3.1558</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9636</v>
+        <v>-1.229</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.8883</v>
+        <v>-2.7144</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1178</v>
+        <v>-1.2646</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.7705</v>
+        <v>-1.4498</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0984</v>
+        <v>-1.2735</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0916</v>
+        <v>-1.3141</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1901</v>
+        <v>0.0406</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.7899</v>
+        <v>-1.441</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2095</v>
+        <v>0.0494</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.5804</v>
+        <v>-1.4904</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3881</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5523</v>
+        <v>0.3881</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5388</v>
+        <v>-0.118</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2412</v>
+        <v>0.058</v>
       </c>
       <c r="U22" t="n">
-        <v>1.78</v>
+        <v>-0.1761</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5382</v>
+        <v>-4.5743</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2212</v>
+        <v>-2.1211</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3169</v>
+        <v>-2.4532</v>
       </c>
       <c r="G23" t="n">
         <v>0.4193</v>
@@ -2248,13 +2248,13 @@
         <v>1.1642</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.819</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3634</v>
+        <v>-0.2633</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4194</v>
+        <v>-0.5557</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4582</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. VILASANCHEZ FREIJOMIL</t>
+          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7396</v>
+        <v>-4.8792</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.456</v>
+        <v>-2.0979</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2835</v>
+        <v>-2.7812</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.7144</v>
+        <v>-3.8883</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2646</v>
+        <v>-0.1178</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4498</v>
+        <v>-3.7705</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2735</v>
+        <v>-0.0984</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.3141</v>
+        <v>1.0916</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0406</v>
+        <v>-1.1901</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.441</v>
+        <v>-3.7899</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0494</v>
+        <v>-1.2095</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4904</v>
+        <v>-2.5804</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5523</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3881</v>
+        <v>1.5523</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4729</v>
+        <v>0.6211</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2423</v>
+        <v>-0.3413</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2306</v>
+        <v>0.9623</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. DOMINGUEZ LORENZO</t>
+          <t>E. BOADA MONTESDEOCA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.4157</v>
+        <v>-5.956</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5363</v>
+        <v>-3.7576</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.8794</v>
+        <v>-2.1984</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.5217</v>
+        <v>-3.4272</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.797</v>
+        <v>-1.6988</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7246</v>
+        <v>-1.7284</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8393</v>
+        <v>-0.2262</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.6106</v>
+        <v>-0.2719</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7713</v>
+        <v>0.0456</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.6824</v>
+        <v>-3.201</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1864</v>
+        <v>-1.427</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.496</v>
+        <v>-1.774</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.3582</v>
+        <v>-2.7164</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.9403</v>
+        <v>-4.8508</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5821</v>
+        <v>2.1344</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0298</v>
+        <v>-0.7063</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2434</v>
+        <v>-0.4686</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2732</v>
+        <v>-0.2378</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.506</v>
+        <v>0.894</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.788</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.506</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E. BOADA MONTESDEOCA</t>
+          <t>P. DOMINGUEZ LORENZO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.511</v>
+        <v>-6.4251</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.258</v>
+        <v>-2.7365</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.2529</v>
+        <v>-3.6886</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.4272</v>
+        <v>-3.5217</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.6988</v>
+        <v>-2.797</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.7284</v>
+        <v>-0.7246</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2262</v>
+        <v>-0.8393</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2719</v>
+        <v>-1.6106</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0456</v>
+        <v>0.7713</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.201</v>
+        <v>-2.6824</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.427</v>
+        <v>-1.1864</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.774</v>
+        <v>-1.496</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.7164</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.8508</v>
+        <v>-1.9403</v>
       </c>
       <c r="R26" t="n">
-        <v>2.1344</v>
+        <v>0.5821</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.2613</v>
+        <v>-0.0393</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9691</v>
+        <v>0.0432</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2923</v>
+        <v>-0.0824</v>
       </c>
       <c r="V26" t="n">
-        <v>0.894</v>
+        <v>-1.506</v>
       </c>
       <c r="W26" t="n">
-        <v>1.788</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.894</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-32.45200000000001</v>
+        <v>-32.4519</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.253</v>
+        <v>-9.253200000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-23.1988</v>
+        <v>-23.1987</v>
       </c>
       <c r="G27" t="n">
         <v>-20.4774</v>
@@ -2533,13 +2533,13 @@
         <v>-10.7888</v>
       </c>
       <c r="J27" t="n">
-        <v>8.939399999999999</v>
+        <v>8.939400000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>3.378000000000001</v>
+        <v>3.378</v>
       </c>
       <c r="L27" t="n">
-        <v>5.561300000000001</v>
+        <v>5.5613</v>
       </c>
       <c r="M27" t="n">
         <v>-29.4168</v>
@@ -2566,16 +2566,16 @@
         <v>-1.6265</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.9195</v>
+        <v>-0.9194999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>2.2134</v>
+        <v>2.213400000000001</v>
       </c>
       <c r="W27" t="n">
         <v>8.657999999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.4448</v>
+        <v>-6.444800000000001</v>
       </c>
     </row>
   </sheetData>
